--- a/meta/17-4-1.xlsx
+++ b/meta/17-4-1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Лист" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -100,41 +100,7 @@
     <t>17.4 Оказывать развивающимся странам помощь в целях обеспечения долгосрочной приемлемости уровня их задолженности благодаря проведению скоординированной политики, направленной на поощрение, в зависимости от обстоятельств, финансирования за счет заемных средств, облегчения долгового бремени и реструктуризации задолженности, и решить проблему внешней задолженности бедных стран с крупной задолженностью, с тем чтобы облегчить их долговое бремя</t>
   </si>
   <si>
-    <t>Министерство финансов Кыргызской Республики (Управление государственного долга)</t>
-  </si>
-  <si>
-    <t>Татиков Р.С.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> r.tatikov@minfin.kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> +996-0312-62-53-13 (доб. 2010, 2023)</t>
-  </si>
-  <si>
     <t>www.minfin.kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Расходы на обслуживание государственного долга (основная сумма + проценты) в качестве доли к экспорту товаров и услуг </t>
-  </si>
-  <si>
-    <t>Обслуживание государственного долга включают операции по выплатам по долговым обязательствам за счет средств соответствующего бюджета.  
-Объем экспорта - стоимость вывезенных из государства за определенное время товаров и услуг.</t>
-  </si>
-  <si>
-    <t>Показатель исчисляется в рамках анализа устойчивости государственного долга. Существуют рекомендуемые МВФ пороговые уровни устойчивости государственного долга для стран с низким уровнем дохода, где соотношение обслуживания внешнего долга к экспорту не должно превышать 15%.
-Данный показатель рассчитывается, как один из показателей при изучении уровня государственного долга и его устойчивости.</t>
-  </si>
-  <si>
-    <t>Данные об объеме экспорта товаров и услуг доступны в Бюллетене НБКР.
-Расходы на обслуживание государственного долга - данные МФ КР.</t>
-  </si>
-  <si>
-    <t>Сбор данных по обслуживанию государственного долга производится по окончанию отчетного периода (года). 
-Данные об объеме экспорта товаров и услуг - из Бюллетеня НБКР.</t>
-  </si>
-  <si>
-    <t>Процентное соотношение расходов на обслуживания государственного долга к объему экспорта товаров и услуг за отчетный период (год).</t>
   </si>
   <si>
     <t>Данный показатель рассчитывается по истечению отчетного периода (на конец года) с 2005 года в годовой динамике.</t>
@@ -148,14 +114,80 @@
  Национальная платформа отчетности ЦУР КР: https://sustainabledevelopment-kyrgyzstan.github.io</t>
   </si>
   <si>
-    <t>17.4.1 Доля поступлений от экспорта товаров и услуг и первичного дохода, расходуемая на обслуживание долга</t>
+    <t>17.4.1 Доля поступлений от экспорта товаров и услуг, расходуемая на обслуживание государственного внешнего долга</t>
+  </si>
+  <si>
+    <t>Абдыбапов А.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +996-0312-62-53-13 (доб. 2010)</t>
+  </si>
+  <si>
+    <t>a.abdybapov@minfin.kg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расходы на обслуживание государственного внешнего долга (основная сумма + проценты) в качестве доли к экспорту товаров и услуг </t>
+  </si>
+  <si>
+    <t>Обслуживание государственного внешнего долга включают операции по выплатам по долговым обязательствам за счет средств соответствующего бюджета.  
+Объем экспорта - стоимость вывезенных из государства за определенное время товаров и услуг.</t>
+  </si>
+  <si>
+    <t>Данные об объеме экспорта товаров и услуг доступны в Бюллетене НБКР.
+Расходы на обслуживание государственного внешнего долга - данные МФ КР.</t>
+  </si>
+  <si>
+    <t>Процентное соотношение расходов на обслуживания государственного внешнего долга к объему экспорта товаров и услуг за отчетный период (год).</t>
+  </si>
+  <si>
+    <t>Министерство финансов Кыргызской Республики (Управление государственного долга и активов)</t>
+  </si>
+  <si>
+    <t>Сбор данных по обслуживанию государственного внешнего долга производится по окончанию отчетного периода (года). 
+Данные об объеме экспорта товаров и услуг -из Бюллетеня НБКР.</t>
+  </si>
+  <si>
+    <r>
+      <t>Показатель исчисляется в рамках анализа устойчивости государственного внешнего долга. Существуют рекомендуемые МВФ пороговые уровни устойчивости государственного внешнего долга для стран с низким уровнем дохода, где соотношение обслуживания</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">государственного </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>внешнего долга к экспорту не должно превышать 15%.
+Данный показатель рассчитывается, как один из показателей при изучении уровня государственного внешнего долга и его устойчивости.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +217,27 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -229,7 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -241,12 +294,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -310,7 +366,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -345,7 +401,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -554,7 +610,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Лист1"/>
+  <sheetPr codeName="Лист1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -573,7 +631,7 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -581,7 +639,7 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -589,173 +647,173 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>42</v>
+      <c r="B4" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>28</v>
+      <c r="B6" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>29</v>
+      <c r="B7" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>30</v>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>32</v>
+      <c r="B10" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>35</v>
+      <c r="B14" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
+      <c r="B16" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>37</v>
+      <c r="B17" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="6"/>
     </row>
     <row r="19" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>38</v>
+      <c r="B19" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="7"/>
     </row>
     <row r="21" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5"/>
+      <c r="B21" s="7"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>39</v>
+      <c r="B23" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>40</v>
+      <c r="B24" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="7"/>
     </row>
     <row r="26" spans="1:2" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>41</v>
+      <c r="B26" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>